--- a/Employee_Reports_wi52/AbdulRashid Byarugaba Q0589.xlsx
+++ b/Employee_Reports_wi52/AbdulRashid Byarugaba Q0589.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-14</v>
+        <v>-22</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1265,11 +1265,11 @@
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -1314,11 +1314,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1363,11 +1363,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1412,11 +1412,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1461,11 +1461,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-24</v>
+        <v>-32</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1510,11 +1510,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-24</v>
+        <v>-32</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-24</v>
+        <v>-32</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1562,78 +1562,78 @@
       <c r="K23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>POWERED ROLLER DECK(matarSOP) (SOPs)</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="3" t="inlineStr"/>
-      <c r="E24" s="3" t="inlineStr"/>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2025</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2026</t>
         </is>
       </c>
-      <c r="H24" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
+      <c r="H24" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>NON POWERED ROLLER DECK(matarSOP) (SOPs)</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2025</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2026</t>
         </is>
       </c>
-      <c r="H25" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr"/>
+      <c r="H25" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
@@ -1658,11 +1658,11 @@
         </is>
       </c>
       <c r="H26" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
@@ -1707,11 +1707,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1735,20 +1735,20 @@
       <c r="E28" s="3" t="inlineStr"/>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>06-Jul-2025</t>
+          <t>23-Aug-2026</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>06-Jul-2027</t>
+          <t>22-Aug-2028</t>
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>320</v>
+        <v>725</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7899</v>
+        <v>7891</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7922</v>
+        <v>7914</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7922</v>
+        <v>7914</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7898</v>
+        <v>7890</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7922</v>
+        <v>7914</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7922</v>
+        <v>7914</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7898</v>
+        <v>7890</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7934</v>
+        <v>7926</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7978</v>
+        <v>7970</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>7978</v>
+        <v>7970</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>7978</v>
+        <v>7970</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>7934</v>
+        <v>7926</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>7978</v>
+        <v>7970</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
